--- a/Сценарий 4_generated.xlsx
+++ b/Сценарий 4_generated.xlsx
@@ -1058,7 +1058,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1592,6 +1592,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="31" fillId="15" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="31" fillId="16" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="32" fillId="15" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="33" fillId="16" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="33" fillId="15" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="14" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3146,19 +3158,19 @@
         </is>
       </c>
       <c r="AM8" s="36" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AN8" s="36" t="n">
-        <v>158.2</v>
+        <v>0</v>
       </c>
       <c r="AO8" s="36" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AP8" s="36" t="n">
-        <v>203.4</v>
+        <v>40.44</v>
       </c>
       <c r="AQ8" s="36" t="n">
-        <v>205</v>
+        <v>41.79</v>
       </c>
     </row>
     <row r="9" ht="15.6" customHeight="1" s="161">
@@ -7554,10 +7566,10 @@
     </row>
     <row r="74">
       <c r="L74" s="27" t="n">
-        <v>126.49</v>
-      </c>
-      <c r="M74" s="79" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M74" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N74" s="29" t="n">
         <v>0</v>
@@ -7566,10 +7578,10 @@
         <v>0</v>
       </c>
       <c r="Q74" s="27" t="n">
-        <v>153.9286</v>
-      </c>
-      <c r="R74" s="79" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R74" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S74" s="29" t="n">
         <v>0</v>
@@ -7578,10 +7590,10 @@
         <v>0</v>
       </c>
       <c r="V74" s="27" t="n">
-        <v>194.6</v>
-      </c>
-      <c r="W74" s="79" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="W74" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X74" s="29" t="n">
         <v>0</v>
@@ -7590,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="AA74" s="27" t="n">
-        <v>197.9082</v>
+        <v>39.34811999999999</v>
       </c>
       <c r="AB74" s="79" t="n">
         <v>1</v>
@@ -7602,7 +7614,7 @@
         <v>0</v>
       </c>
       <c r="AF74" s="27" t="n">
-        <v>203.4</v>
+        <v>40.44</v>
       </c>
       <c r="AG74" s="28" t="n">
         <v>1</v>
@@ -7616,10 +7628,10 @@
     </row>
     <row r="75">
       <c r="L75" s="31" t="n">
-        <v>126.841</v>
-      </c>
-      <c r="M75" s="79" t="n">
-        <v>1.002774922918808</v>
+        <v>0</v>
+      </c>
+      <c r="M75" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N75" s="33" t="n">
         <v>0.1</v>
@@ -7628,10 +7640,10 @@
         <v>0</v>
       </c>
       <c r="Q75" s="31" t="n">
-        <v>154.35574</v>
-      </c>
-      <c r="R75" s="79" t="n">
-        <v>1.002774922918808</v>
+        <v>0</v>
+      </c>
+      <c r="R75" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S75" s="33" t="n">
         <v>0.1</v>
@@ -7640,10 +7652,10 @@
         <v>0</v>
       </c>
       <c r="V75" s="31" t="n">
-        <v>195.14</v>
-      </c>
-      <c r="W75" s="79" t="n">
-        <v>1.002774922918808</v>
+        <v>0</v>
+      </c>
+      <c r="W75" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X75" s="33" t="n">
         <v>0.1</v>
@@ -7652,7 +7664,7 @@
         <v>0</v>
       </c>
       <c r="AA75" s="31" t="n">
-        <v>198.45738</v>
+        <v>39.457308</v>
       </c>
       <c r="AB75" s="79" t="n">
         <v>1.002774922918808</v>
@@ -7664,10 +7676,10 @@
         <v>0</v>
       </c>
       <c r="AF75" s="31" t="n">
-        <v>203.56</v>
+        <v>40.575</v>
       </c>
       <c r="AG75" s="32" t="n">
-        <v>1.0007866273353</v>
+        <v>1.003338278931751</v>
       </c>
       <c r="AH75" s="33" t="n">
         <v>0.1</v>
@@ -7678,10 +7690,10 @@
     </row>
     <row r="76">
       <c r="L76" s="31" t="n">
-        <v>127.192</v>
-      </c>
-      <c r="M76" s="79" t="n">
-        <v>1.005549845837616</v>
+        <v>0</v>
+      </c>
+      <c r="M76" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N76" s="33" t="n">
         <v>0.2</v>
@@ -7690,10 +7702,10 @@
         <v>0</v>
       </c>
       <c r="Q76" s="31" t="n">
-        <v>154.78288</v>
-      </c>
-      <c r="R76" s="79" t="n">
-        <v>1.005549845837616</v>
+        <v>0</v>
+      </c>
+      <c r="R76" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S76" s="33" t="n">
         <v>0.2</v>
@@ -7702,10 +7714,10 @@
         <v>0</v>
       </c>
       <c r="V76" s="31" t="n">
-        <v>195.68</v>
-      </c>
-      <c r="W76" s="79" t="n">
-        <v>1.005549845837616</v>
+        <v>0</v>
+      </c>
+      <c r="W76" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X76" s="33" t="n">
         <v>0.2</v>
@@ -7714,7 +7726,7 @@
         <v>0</v>
       </c>
       <c r="AA76" s="31" t="n">
-        <v>199.00656</v>
+        <v>39.566496</v>
       </c>
       <c r="AB76" s="79" t="n">
         <v>1.005549845837616</v>
@@ -7726,10 +7738,10 @@
         <v>0</v>
       </c>
       <c r="AF76" s="31" t="n">
-        <v>203.72</v>
+        <v>40.70999999999999</v>
       </c>
       <c r="AG76" s="32" t="n">
-        <v>1.0015732546706</v>
+        <v>1.006676557863501</v>
       </c>
       <c r="AH76" s="33" t="n">
         <v>0.2</v>
@@ -7740,10 +7752,10 @@
     </row>
     <row r="77">
       <c r="L77" s="31" t="n">
-        <v>127.543</v>
-      </c>
-      <c r="M77" s="79" t="n">
-        <v>1.008324768756423</v>
+        <v>0</v>
+      </c>
+      <c r="M77" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N77" s="33" t="n">
         <v>0.3</v>
@@ -7752,10 +7764,10 @@
         <v>0</v>
       </c>
       <c r="Q77" s="31" t="n">
-        <v>155.21002</v>
-      </c>
-      <c r="R77" s="79" t="n">
-        <v>1.008324768756424</v>
+        <v>0</v>
+      </c>
+      <c r="R77" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S77" s="33" t="n">
         <v>0.3</v>
@@ -7764,10 +7776,10 @@
         <v>0</v>
       </c>
       <c r="V77" s="31" t="n">
-        <v>196.22</v>
-      </c>
-      <c r="W77" s="79" t="n">
-        <v>1.008324768756423</v>
+        <v>0</v>
+      </c>
+      <c r="W77" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X77" s="33" t="n">
         <v>0.3</v>
@@ -7776,7 +7788,7 @@
         <v>0</v>
       </c>
       <c r="AA77" s="31" t="n">
-        <v>199.55574</v>
+        <v>39.675684</v>
       </c>
       <c r="AB77" s="79" t="n">
         <v>1.008324768756424</v>
@@ -7788,10 +7800,10 @@
         <v>0</v>
       </c>
       <c r="AF77" s="31" t="n">
-        <v>203.88</v>
+        <v>40.84499999999999</v>
       </c>
       <c r="AG77" s="32" t="n">
-        <v>1.0023598820059</v>
+        <v>1.010014836795252</v>
       </c>
       <c r="AH77" s="33" t="n">
         <v>0.3</v>
@@ -7802,10 +7814,10 @@
     </row>
     <row r="78">
       <c r="L78" s="31" t="n">
-        <v>127.894</v>
-      </c>
-      <c r="M78" s="79" t="n">
-        <v>1.011099691675231</v>
+        <v>0</v>
+      </c>
+      <c r="M78" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N78" s="33" t="n">
         <v>0.4</v>
@@ -7814,10 +7826,10 @@
         <v>0</v>
       </c>
       <c r="Q78" s="31" t="n">
-        <v>155.63716</v>
-      </c>
-      <c r="R78" s="79" t="n">
-        <v>1.011099691675232</v>
+        <v>0</v>
+      </c>
+      <c r="R78" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S78" s="33" t="n">
         <v>0.4</v>
@@ -7826,10 +7838,10 @@
         <v>0</v>
       </c>
       <c r="V78" s="31" t="n">
-        <v>196.76</v>
-      </c>
-      <c r="W78" s="79" t="n">
-        <v>1.011099691675231</v>
+        <v>0</v>
+      </c>
+      <c r="W78" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X78" s="33" t="n">
         <v>0.4</v>
@@ -7838,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AA78" s="31" t="n">
-        <v>200.10492</v>
+        <v>39.78487200000001</v>
       </c>
       <c r="AB78" s="79" t="n">
-        <v>1.011099691675231</v>
+        <v>1.011099691675232</v>
       </c>
       <c r="AC78" s="33" t="n">
         <v>0.4</v>
@@ -7850,10 +7862,10 @@
         <v>0</v>
       </c>
       <c r="AF78" s="31" t="n">
-        <v>204.04</v>
+        <v>40.97999999999999</v>
       </c>
       <c r="AG78" s="32" t="n">
-        <v>1.0031465093412</v>
+        <v>1.013353115727003</v>
       </c>
       <c r="AH78" s="33" t="n">
         <v>0.4</v>
@@ -7864,10 +7876,10 @@
     </row>
     <row r="79">
       <c r="L79" s="31" t="n">
-        <v>128.245</v>
-      </c>
-      <c r="M79" s="79" t="n">
-        <v>1.013874614594039</v>
+        <v>0</v>
+      </c>
+      <c r="M79" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N79" s="33" t="n">
         <v>0.5</v>
@@ -7876,10 +7888,10 @@
         <v>0</v>
       </c>
       <c r="Q79" s="31" t="n">
-        <v>156.0643</v>
-      </c>
-      <c r="R79" s="79" t="n">
-        <v>1.013874614594039</v>
+        <v>0</v>
+      </c>
+      <c r="R79" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S79" s="33" t="n">
         <v>0.5</v>
@@ -7888,10 +7900,10 @@
         <v>0</v>
       </c>
       <c r="V79" s="31" t="n">
-        <v>197.3</v>
-      </c>
-      <c r="W79" s="79" t="n">
-        <v>1.013874614594039</v>
+        <v>0</v>
+      </c>
+      <c r="W79" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X79" s="33" t="n">
         <v>0.5</v>
@@ -7900,7 +7912,7 @@
         <v>0</v>
       </c>
       <c r="AA79" s="31" t="n">
-        <v>200.6541</v>
+        <v>39.89406000000001</v>
       </c>
       <c r="AB79" s="79" t="n">
         <v>1.013874614594039</v>
@@ -7912,10 +7924,10 @@
         <v>0</v>
       </c>
       <c r="AF79" s="31" t="n">
-        <v>204.2</v>
+        <v>41.11499999999999</v>
       </c>
       <c r="AG79" s="32" t="n">
-        <v>1.003933136676499</v>
+        <v>1.016691394658753</v>
       </c>
       <c r="AH79" s="33" t="n">
         <v>0.5</v>
@@ -7926,10 +7938,10 @@
     </row>
     <row r="80">
       <c r="L80" s="31" t="n">
-        <v>128.596</v>
-      </c>
-      <c r="M80" s="79" t="n">
-        <v>1.016649537512847</v>
+        <v>0</v>
+      </c>
+      <c r="M80" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N80" s="33" t="n">
         <v>0.6</v>
@@ -7938,10 +7950,10 @@
         <v>0</v>
       </c>
       <c r="Q80" s="31" t="n">
-        <v>156.49144</v>
-      </c>
-      <c r="R80" s="79" t="n">
-        <v>1.016649537512847</v>
+        <v>0</v>
+      </c>
+      <c r="R80" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S80" s="33" t="n">
         <v>0.6</v>
@@ -7950,10 +7962,10 @@
         <v>0</v>
       </c>
       <c r="V80" s="31" t="n">
-        <v>197.8399999999999</v>
-      </c>
-      <c r="W80" s="79" t="n">
-        <v>1.016649537512847</v>
+        <v>0</v>
+      </c>
+      <c r="W80" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X80" s="33" t="n">
         <v>0.6</v>
@@ -7962,7 +7974,7 @@
         <v>0</v>
       </c>
       <c r="AA80" s="31" t="n">
-        <v>201.20328</v>
+        <v>40.00324800000001</v>
       </c>
       <c r="AB80" s="79" t="n">
         <v>1.016649537512847</v>
@@ -7974,10 +7986,10 @@
         <v>0</v>
       </c>
       <c r="AF80" s="31" t="n">
-        <v>204.36</v>
+        <v>41.24999999999999</v>
       </c>
       <c r="AG80" s="32" t="n">
-        <v>1.004719764011799</v>
+        <v>1.020029673590504</v>
       </c>
       <c r="AH80" s="33" t="n">
         <v>0.6</v>
@@ -7988,10 +8000,10 @@
     </row>
     <row r="81">
       <c r="L81" s="31" t="n">
-        <v>128.947</v>
-      </c>
-      <c r="M81" s="79" t="n">
-        <v>1.019424460431655</v>
+        <v>0</v>
+      </c>
+      <c r="M81" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N81" s="33" t="n">
         <v>0.7</v>
@@ -8000,10 +8012,10 @@
         <v>0</v>
       </c>
       <c r="Q81" s="31" t="n">
-        <v>156.91858</v>
-      </c>
-      <c r="R81" s="79" t="n">
-        <v>1.019424460431655</v>
+        <v>0</v>
+      </c>
+      <c r="R81" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S81" s="33" t="n">
         <v>0.7</v>
@@ -8012,10 +8024,10 @@
         <v>0</v>
       </c>
       <c r="V81" s="31" t="n">
-        <v>198.3799999999999</v>
-      </c>
-      <c r="W81" s="79" t="n">
-        <v>1.019424460431654</v>
+        <v>0</v>
+      </c>
+      <c r="W81" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X81" s="33" t="n">
         <v>0.7</v>
@@ -8024,7 +8036,7 @@
         <v>0</v>
       </c>
       <c r="AA81" s="31" t="n">
-        <v>201.75246</v>
+        <v>40.11243600000002</v>
       </c>
       <c r="AB81" s="79" t="n">
         <v>1.019424460431655</v>
@@ -8036,10 +8048,10 @@
         <v>0</v>
       </c>
       <c r="AF81" s="31" t="n">
-        <v>204.52</v>
+        <v>41.38499999999998</v>
       </c>
       <c r="AG81" s="32" t="n">
-        <v>1.005506391347099</v>
+        <v>1.023367952522255</v>
       </c>
       <c r="AH81" s="33" t="n">
         <v>0.7</v>
@@ -8050,10 +8062,10 @@
     </row>
     <row r="82">
       <c r="L82" s="31" t="n">
-        <v>129.298</v>
-      </c>
-      <c r="M82" s="79" t="n">
-        <v>1.022199383350463</v>
+        <v>0</v>
+      </c>
+      <c r="M82" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N82" s="33" t="n">
         <v>0.8</v>
@@ -8062,10 +8074,10 @@
         <v>0</v>
       </c>
       <c r="Q82" s="31" t="n">
-        <v>157.3457200000001</v>
-      </c>
-      <c r="R82" s="79" t="n">
-        <v>1.022199383350463</v>
+        <v>0</v>
+      </c>
+      <c r="R82" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S82" s="33" t="n">
         <v>0.8</v>
@@ -8074,10 +8086,10 @@
         <v>0</v>
       </c>
       <c r="V82" s="31" t="n">
-        <v>198.9199999999999</v>
-      </c>
-      <c r="W82" s="79" t="n">
-        <v>1.022199383350462</v>
+        <v>0</v>
+      </c>
+      <c r="W82" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X82" s="33" t="n">
         <v>0.8</v>
@@ -8086,7 +8098,7 @@
         <v>0</v>
       </c>
       <c r="AA82" s="31" t="n">
-        <v>202.30164</v>
+        <v>40.22162400000002</v>
       </c>
       <c r="AB82" s="79" t="n">
         <v>1.022199383350463</v>
@@ -8098,10 +8110,10 @@
         <v>0</v>
       </c>
       <c r="AF82" s="31" t="n">
-        <v>204.68</v>
+        <v>41.51999999999998</v>
       </c>
       <c r="AG82" s="32" t="n">
-        <v>1.006293018682399</v>
+        <v>1.026706231454006</v>
       </c>
       <c r="AH82" s="33" t="n">
         <v>0.8</v>
@@ -8112,10 +8124,10 @@
     </row>
     <row r="83">
       <c r="L83" s="31" t="n">
-        <v>129.649</v>
-      </c>
-      <c r="M83" s="79" t="n">
-        <v>1.02497430626927</v>
+        <v>0</v>
+      </c>
+      <c r="M83" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N83" s="33" t="n">
         <v>0.9</v>
@@ -8124,10 +8136,10 @@
         <v>0</v>
       </c>
       <c r="Q83" s="31" t="n">
-        <v>157.7728600000001</v>
-      </c>
-      <c r="R83" s="79" t="n">
-        <v>1.024974306269271</v>
+        <v>0</v>
+      </c>
+      <c r="R83" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S83" s="33" t="n">
         <v>0.9</v>
@@ -8136,10 +8148,10 @@
         <v>0</v>
       </c>
       <c r="V83" s="31" t="n">
-        <v>199.4599999999999</v>
-      </c>
-      <c r="W83" s="79" t="n">
-        <v>1.02497430626927</v>
+        <v>0</v>
+      </c>
+      <c r="W83" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X83" s="33" t="n">
         <v>0.9</v>
@@ -8148,7 +8160,7 @@
         <v>0</v>
       </c>
       <c r="AA83" s="31" t="n">
-        <v>202.8508200000001</v>
+        <v>40.33081200000002</v>
       </c>
       <c r="AB83" s="79" t="n">
         <v>1.024974306269271</v>
@@ -8160,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AF83" s="31" t="n">
-        <v>204.84</v>
+        <v>41.65499999999998</v>
       </c>
       <c r="AG83" s="32" t="n">
-        <v>1.007079646017699</v>
+        <v>1.030044510385756</v>
       </c>
       <c r="AH83" s="33" t="n">
         <v>0.9</v>
@@ -8174,10 +8186,10 @@
     </row>
     <row r="84">
       <c r="L84" s="78" t="n">
-        <v>130</v>
-      </c>
-      <c r="M84" s="79" t="n">
-        <v>1.027749229188078</v>
+        <v>0</v>
+      </c>
+      <c r="M84" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N84" s="41" t="n">
         <v>1</v>
@@ -8186,10 +8198,10 @@
         <v>0</v>
       </c>
       <c r="Q84" s="78" t="n">
-        <v>158.2</v>
-      </c>
-      <c r="R84" s="79" t="n">
-        <v>1.027749229188078</v>
+        <v>0</v>
+      </c>
+      <c r="R84" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S84" s="41" t="n">
         <v>1</v>
@@ -8198,10 +8210,10 @@
         <v>0</v>
       </c>
       <c r="V84" s="78" t="n">
-        <v>200</v>
-      </c>
-      <c r="W84" s="79" t="n">
-        <v>1.027749229188078</v>
+        <v>0</v>
+      </c>
+      <c r="W84" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X84" s="41" t="n">
         <v>1</v>
@@ -8210,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="AA84" s="78" t="n">
-        <v>203.4</v>
+        <v>40.44</v>
       </c>
       <c r="AB84" s="79" t="n">
         <v>1.027749229188078</v>
@@ -8222,10 +8234,10 @@
         <v>0</v>
       </c>
       <c r="AF84" s="78" t="n">
-        <v>205</v>
+        <v>41.79</v>
       </c>
       <c r="AG84" s="81" t="n">
-        <v>1.007866273352999</v>
+        <v>1.033382789317507</v>
       </c>
       <c r="AH84" s="41" t="n">
         <v>1</v>
@@ -32371,7 +32383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J148"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="161" min="1" max="1"/>
@@ -32390,7 +32402,7 @@
       <c r="A1" s="188" t="inlineStr"/>
       <c r="B1" s="189" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Total PN</t>
         </is>
       </c>
       <c r="C1" s="190" t="inlineStr">
@@ -32560,13 +32572,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="195" t="n">
-        <v>0.1</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F5" s="195" t="n">
         <v>0.09000000000000001</v>
       </c>
       <c r="G5" s="195" t="n">
-        <v>0.05076923076923078</v>
+        <v>0.04846153846153847</v>
       </c>
       <c r="H5" s="195" t="n">
         <v>0</v>
@@ -32575,7 +32587,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="196" t="n">
-        <v>0.05076923076923078</v>
+        <v>0.04846153846153847</v>
       </c>
     </row>
     <row r="6">
@@ -32644,10 +32656,10 @@
         <v>0</v>
       </c>
       <c r="I7" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="J7" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="8">
@@ -32659,22 +32671,22 @@
         <v>0.27</v>
       </c>
       <c r="E8" s="198" t="n">
-        <v>0.295</v>
+        <v>0.285</v>
       </c>
       <c r="F8" s="198" t="n">
         <v>0.285</v>
       </c>
       <c r="G8" s="198" t="n">
-        <v>0.2778007655851258</v>
+        <v>0.2754930732774335</v>
       </c>
       <c r="H8" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="198" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="J8" s="198" t="n">
-        <v>0.4778007655851259</v>
+        <v>0.4054930732774334</v>
       </c>
     </row>
     <row r="9"/>
@@ -32683,7 +32695,7 @@
       <c r="A11" s="188" t="inlineStr"/>
       <c r="B11" s="189" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="C11" s="190" t="inlineStr">
@@ -32784,10 +32796,10 @@
         <v>0.1</v>
       </c>
       <c r="F13" s="195" t="n">
-        <v>0.07742890995260657</v>
+        <v>0.1</v>
       </c>
       <c r="G13" s="195" t="n">
-        <v>0.04690120306234048</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="H13" s="195" t="n">
         <v>0</v>
@@ -32796,7 +32808,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="196" t="n">
-        <v>0.04690120306234048</v>
+        <v>0.05384615384615385</v>
       </c>
     </row>
     <row r="14">
@@ -32856,10 +32868,10 @@
         <v>0.1</v>
       </c>
       <c r="F15" s="195" t="n">
-        <v>0.1</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="G15" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.05076923076923078</v>
       </c>
       <c r="H15" s="195" t="n">
         <v>0</v>
@@ -32868,7 +32880,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="196" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.05076923076923078</v>
       </c>
     </row>
     <row r="16">
@@ -32937,10 +32949,10 @@
         <v>0</v>
       </c>
       <c r="I17" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="J17" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="18">
@@ -32955,19 +32967,19 @@
         <v>0.295</v>
       </c>
       <c r="F18" s="198" t="n">
-        <v>0.2724289099526066</v>
+        <v>0.285</v>
       </c>
       <c r="G18" s="198" t="n">
-        <v>0.2739327378782355</v>
+        <v>0.2778007655851258</v>
       </c>
       <c r="H18" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="198" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="J18" s="198" t="n">
-        <v>0.4739327378782355</v>
+        <v>0.4078007655851258</v>
       </c>
     </row>
     <row r="19"/>
@@ -32976,7 +32988,7 @@
       <c r="A21" s="188" t="inlineStr"/>
       <c r="B21" s="189" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C21" s="190" t="inlineStr">
@@ -33077,10 +33089,10 @@
         <v>0.1</v>
       </c>
       <c r="F23" s="195" t="n">
-        <v>0.1</v>
+        <v>0.07742890995260657</v>
       </c>
       <c r="G23" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04690120306234048</v>
       </c>
       <c r="H23" s="195" t="n">
         <v>0</v>
@@ -33089,7 +33101,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="196" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04690120306234048</v>
       </c>
     </row>
     <row r="24">
@@ -33146,13 +33158,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="195" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="F25" s="195" t="n">
         <v>0.1</v>
       </c>
       <c r="G25" s="195" t="n">
-        <v>0.05153846153846154</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="H25" s="195" t="n">
         <v>0</v>
@@ -33161,7 +33173,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="196" t="n">
-        <v>0.05153846153846154</v>
+        <v>0.05384615384615385</v>
       </c>
     </row>
     <row r="26">
@@ -33230,10 +33242,10 @@
         <v>0</v>
       </c>
       <c r="I27" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="J27" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="28">
@@ -33245,22 +33257,22 @@
         <v>0.27</v>
       </c>
       <c r="E28" s="198" t="n">
-        <v>0.285</v>
+        <v>0.295</v>
       </c>
       <c r="F28" s="198" t="n">
-        <v>0.295</v>
+        <v>0.2724289099526066</v>
       </c>
       <c r="G28" s="198" t="n">
-        <v>0.2785699963543566</v>
+        <v>0.2739327378782355</v>
       </c>
       <c r="H28" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="198" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="J28" s="198" t="n">
-        <v>0.4785699963543566</v>
+        <v>0.4039327378782355</v>
       </c>
     </row>
     <row r="29"/>
@@ -33269,7 +33281,7 @@
       <c r="A31" s="188" t="inlineStr"/>
       <c r="B31" s="189" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="C31" s="190" t="inlineStr">
@@ -33439,13 +33451,13 @@
         <v>0</v>
       </c>
       <c r="E35" s="195" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F35" s="195" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="G35" s="195" t="n">
-        <v>0.03769230769230768</v>
+        <v>0.05153846153846154</v>
       </c>
       <c r="H35" s="195" t="n">
         <v>0</v>
@@ -33454,7 +33466,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="196" t="n">
-        <v>0.03769230769230768</v>
+        <v>0.05153846153846154</v>
       </c>
     </row>
     <row r="36">
@@ -33523,10 +33535,10 @@
         <v>0</v>
       </c>
       <c r="I37" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="J37" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="38">
@@ -33538,22 +33550,22 @@
         <v>0.27</v>
       </c>
       <c r="E38" s="198" t="n">
-        <v>0.265</v>
+        <v>0.285</v>
       </c>
       <c r="F38" s="198" t="n">
-        <v>0.265</v>
+        <v>0.295</v>
       </c>
       <c r="G38" s="198" t="n">
-        <v>0.2647238425082027</v>
+        <v>0.2785699963543566</v>
       </c>
       <c r="H38" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="198" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="J38" s="198" t="n">
-        <v>0.4647238425082028</v>
+        <v>0.4085699963543565</v>
       </c>
     </row>
     <row r="39"/>
@@ -33562,7 +33574,7 @@
       <c r="A41" s="188" t="inlineStr"/>
       <c r="B41" s="189" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C41" s="190" t="inlineStr">
@@ -33732,13 +33744,13 @@
         <v>0</v>
       </c>
       <c r="E45" s="195" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F45" s="195" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="G45" s="195" t="n">
-        <v>0.04846153846153847</v>
+        <v>0.03769230769230768</v>
       </c>
       <c r="H45" s="195" t="n">
         <v>0</v>
@@ -33747,7 +33759,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="196" t="n">
-        <v>0.04846153846153847</v>
+        <v>0.03769230769230768</v>
       </c>
     </row>
     <row r="46">
@@ -33816,10 +33828,10 @@
         <v>0</v>
       </c>
       <c r="I47" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="J47" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="48">
@@ -33831,22 +33843,22 @@
         <v>0.27</v>
       </c>
       <c r="E48" s="198" t="n">
-        <v>0.285</v>
+        <v>0.265</v>
       </c>
       <c r="F48" s="198" t="n">
-        <v>0.285</v>
+        <v>0.265</v>
       </c>
       <c r="G48" s="198" t="n">
-        <v>0.2754930732774335</v>
+        <v>0.2647238425082027</v>
       </c>
       <c r="H48" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="198" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="J48" s="198" t="n">
-        <v>0.4754930732774335</v>
+        <v>0.3947238425082027</v>
       </c>
     </row>
     <row r="49"/>
@@ -33855,7 +33867,7 @@
       <c r="A51" s="188" t="inlineStr"/>
       <c r="B51" s="189" t="inlineStr">
         <is>
-          <t>Siberia</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="C51" s="190" t="inlineStr">
@@ -34025,13 +34037,13 @@
         <v>0</v>
       </c>
       <c r="E55" s="195" t="n">
-        <v>0.1</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F55" s="195" t="n">
-        <v>0.1</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="G55" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04846153846153847</v>
       </c>
       <c r="H55" s="195" t="n">
         <v>0</v>
@@ -34040,7 +34052,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="196" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04846153846153847</v>
       </c>
     </row>
     <row r="56">
@@ -34109,10 +34121,10 @@
         <v>0</v>
       </c>
       <c r="I57" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="J57" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="58">
@@ -34124,22 +34136,22 @@
         <v>0.27</v>
       </c>
       <c r="E58" s="198" t="n">
-        <v>0.295</v>
+        <v>0.285</v>
       </c>
       <c r="F58" s="198" t="n">
-        <v>0.295</v>
+        <v>0.285</v>
       </c>
       <c r="G58" s="198" t="n">
-        <v>0.2808776886620489</v>
+        <v>0.2754930732774335</v>
       </c>
       <c r="H58" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="198" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="J58" s="198" t="n">
-        <v>0.4808776886620489</v>
+        <v>0.4054930732774334</v>
       </c>
     </row>
     <row r="59"/>
@@ -34148,7 +34160,7 @@
       <c r="A61" s="188" t="inlineStr"/>
       <c r="B61" s="189" t="inlineStr">
         <is>
-          <t>Far East</t>
+          <t>Siberia</t>
         </is>
       </c>
       <c r="C61" s="190" t="inlineStr">
@@ -34318,13 +34330,13 @@
         <v>0</v>
       </c>
       <c r="E65" s="195" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="F65" s="195" t="n">
         <v>0.1</v>
       </c>
       <c r="G65" s="195" t="n">
-        <v>0.05153846153846154</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="H65" s="195" t="n">
         <v>0</v>
@@ -34333,7 +34345,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="196" t="n">
-        <v>0.05153846153846154</v>
+        <v>0.05384615384615385</v>
       </c>
     </row>
     <row r="66">
@@ -34402,10 +34414,10 @@
         <v>0</v>
       </c>
       <c r="I67" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="J67" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="68">
@@ -34417,22 +34429,22 @@
         <v>0.27</v>
       </c>
       <c r="E68" s="198" t="n">
-        <v>0.285</v>
+        <v>0.295</v>
       </c>
       <c r="F68" s="198" t="n">
         <v>0.295</v>
       </c>
       <c r="G68" s="198" t="n">
-        <v>0.2785699963543566</v>
+        <v>0.2808776886620489</v>
       </c>
       <c r="H68" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="198" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="J68" s="198" t="n">
-        <v>0.4785699963543566</v>
+        <v>0.4108776886620489</v>
       </c>
     </row>
     <row r="69"/>
@@ -34441,7 +34453,7 @@
       <c r="A71" s="188" t="inlineStr"/>
       <c r="B71" s="189" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>Far East</t>
         </is>
       </c>
       <c r="C71" s="190" t="inlineStr">
@@ -34539,13 +34551,13 @@
         <v>0</v>
       </c>
       <c r="E73" s="195" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F73" s="195" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G73" s="195" t="n">
-        <v>0</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="H73" s="195" t="n">
         <v>0</v>
@@ -34554,7 +34566,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="196" t="n">
-        <v>0</v>
+        <v>0.05384615384615385</v>
       </c>
     </row>
     <row r="74">
@@ -34611,13 +34623,13 @@
         <v>0</v>
       </c>
       <c r="E75" s="195" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F75" s="195" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="G75" s="195" t="n">
-        <v>0.03692307692307693</v>
+        <v>0.05153846153846154</v>
       </c>
       <c r="H75" s="195" t="n">
         <v>0</v>
@@ -34626,7 +34638,7 @@
         <v>0</v>
       </c>
       <c r="J75" s="196" t="n">
-        <v>0.03692307692307693</v>
+        <v>0.05153846153846154</v>
       </c>
     </row>
     <row r="76">
@@ -34695,10 +34707,10 @@
         <v>0</v>
       </c>
       <c r="I77" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="J77" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="78">
@@ -34710,22 +34722,22 @@
         <v>0.27</v>
       </c>
       <c r="E78" s="198" t="n">
-        <v>0.175</v>
+        <v>0.285</v>
       </c>
       <c r="F78" s="198" t="n">
-        <v>0.155</v>
+        <v>0.295</v>
       </c>
       <c r="G78" s="198" t="n">
-        <v>0.2101084578928181</v>
+        <v>0.2785699963543566</v>
       </c>
       <c r="H78" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I78" s="198" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="J78" s="198" t="n">
-        <v>0.4101084578928181</v>
+        <v>0.4085699963543565</v>
       </c>
     </row>
     <row r="79"/>
@@ -34734,7 +34746,7 @@
       <c r="A81" s="188" t="inlineStr"/>
       <c r="B81" s="189" t="inlineStr">
         <is>
-          <t>D-Com</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="C81" s="190" t="inlineStr">
@@ -34832,13 +34844,13 @@
         <v>0</v>
       </c>
       <c r="E83" s="195" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F83" s="195" t="n">
-        <v>0.08507109004739344</v>
+        <v>0</v>
       </c>
       <c r="G83" s="195" t="n">
-        <v>0.04925264309150568</v>
+        <v>0</v>
       </c>
       <c r="H83" s="195" t="n">
         <v>0</v>
@@ -34847,7 +34859,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="196" t="n">
-        <v>0.04925264309150568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -34904,13 +34916,13 @@
         <v>0</v>
       </c>
       <c r="E85" s="195" t="n">
-        <v>0</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="F85" s="195" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G85" s="195" t="n">
-        <v>0.006153846153846155</v>
+        <v>0.03692307692307693</v>
       </c>
       <c r="H85" s="195" t="n">
         <v>0</v>
@@ -34919,7 +34931,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="196" t="n">
-        <v>0.006153846153846155</v>
+        <v>0.03692307692307693</v>
       </c>
     </row>
     <row r="86">
@@ -34988,10 +35000,10 @@
         <v>0</v>
       </c>
       <c r="I87" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="J87" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="88">
@@ -35003,22 +35015,22 @@
         <v>0.27</v>
       </c>
       <c r="E88" s="198" t="n">
-        <v>0.195</v>
+        <v>0.175</v>
       </c>
       <c r="F88" s="198" t="n">
-        <v>0.2000710900473934</v>
+        <v>0.155</v>
       </c>
       <c r="G88" s="198" t="n">
-        <v>0.228591870215093</v>
+        <v>0.2101084578928181</v>
       </c>
       <c r="H88" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I88" s="198" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="J88" s="198" t="n">
-        <v>0.428591870215093</v>
+        <v>0.3401084578928181</v>
       </c>
     </row>
     <row r="89"/>
@@ -35027,7 +35039,7 @@
       <c r="A91" s="188" t="inlineStr"/>
       <c r="B91" s="189" t="inlineStr">
         <is>
-          <t>Любимчик 2.0</t>
+          <t>D-Com</t>
         </is>
       </c>
       <c r="C91" s="190" t="inlineStr">
@@ -35128,10 +35140,10 @@
         <v>0.1</v>
       </c>
       <c r="F93" s="195" t="n">
-        <v>0.1</v>
+        <v>0.08507109004739344</v>
       </c>
       <c r="G93" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04925264309150568</v>
       </c>
       <c r="H93" s="195" t="n">
         <v>0</v>
@@ -35140,7 +35152,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="196" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04925264309150568</v>
       </c>
     </row>
     <row r="94">
@@ -35200,10 +35212,10 @@
         <v>0</v>
       </c>
       <c r="F95" s="195" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G95" s="195" t="n">
-        <v>0</v>
+        <v>0.006153846153846155</v>
       </c>
       <c r="H95" s="195" t="n">
         <v>0</v>
@@ -35212,7 +35224,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="196" t="n">
-        <v>0</v>
+        <v>0.006153846153846155</v>
       </c>
     </row>
     <row r="96">
@@ -35281,10 +35293,10 @@
         <v>0</v>
       </c>
       <c r="I97" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="J97" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="98">
@@ -35299,19 +35311,19 @@
         <v>0.195</v>
       </c>
       <c r="F98" s="198" t="n">
-        <v>0.195</v>
+        <v>0.2000710900473934</v>
       </c>
       <c r="G98" s="198" t="n">
-        <v>0.227031534815895</v>
+        <v>0.228591870215093</v>
       </c>
       <c r="H98" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I98" s="198" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="J98" s="198" t="n">
-        <v>0.4270315348158951</v>
+        <v>0.358591870215093</v>
       </c>
     </row>
     <row r="99"/>
@@ -35320,7 +35332,7 @@
       <c r="A101" s="188" t="inlineStr"/>
       <c r="B101" s="189" t="inlineStr">
         <is>
-          <t>X5</t>
+          <t>Любимчик 2.0</t>
         </is>
       </c>
       <c r="C101" s="190" t="inlineStr">
@@ -35490,13 +35502,13 @@
         <v>0</v>
       </c>
       <c r="E105" s="195" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F105" s="195" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G105" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0</v>
       </c>
       <c r="H105" s="195" t="n">
         <v>0</v>
@@ -35505,7 +35517,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="196" t="n">
-        <v>0.05384615384615385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -35574,10 +35586,10 @@
         <v>0</v>
       </c>
       <c r="I107" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="J107" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="108">
@@ -35589,22 +35601,22 @@
         <v>0.27</v>
       </c>
       <c r="E108" s="198" t="n">
-        <v>0.295</v>
+        <v>0.195</v>
       </c>
       <c r="F108" s="198" t="n">
-        <v>0.295</v>
+        <v>0.195</v>
       </c>
       <c r="G108" s="198" t="n">
-        <v>0.2808776886620489</v>
+        <v>0.227031534815895</v>
       </c>
       <c r="H108" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I108" s="198" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="J108" s="198" t="n">
-        <v>0.4808776886620489</v>
+        <v>0.357031534815895</v>
       </c>
     </row>
     <row r="109"/>
@@ -35613,7 +35625,7 @@
       <c r="A111" s="188" t="inlineStr"/>
       <c r="B111" s="189" t="inlineStr">
         <is>
-          <t>Magnit &amp; Dixy</t>
+          <t>X5</t>
         </is>
       </c>
       <c r="C111" s="190" t="inlineStr">
@@ -35711,13 +35723,13 @@
         <v>0</v>
       </c>
       <c r="E113" s="195" t="n">
-        <v>0.08507109004739344</v>
+        <v>0.1</v>
       </c>
       <c r="F113" s="195" t="n">
-        <v>0.04739336492891005</v>
+        <v>0.1</v>
       </c>
       <c r="G113" s="195" t="n">
-        <v>0.03421436383521696</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="H113" s="195" t="n">
         <v>0</v>
@@ -35726,7 +35738,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="196" t="n">
-        <v>0.03421436383521696</v>
+        <v>0.05384615384615385</v>
       </c>
     </row>
     <row r="114">
@@ -35783,13 +35795,13 @@
         <v>0</v>
       </c>
       <c r="E115" s="195" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="F115" s="195" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="G115" s="195" t="n">
-        <v>0.04538461538461539</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="H115" s="195" t="n">
         <v>0</v>
@@ -35798,7 +35810,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="196" t="n">
-        <v>0.04538461538461539</v>
+        <v>0.05384615384615385</v>
       </c>
     </row>
     <row r="116">
@@ -35867,10 +35879,10 @@
         <v>0</v>
       </c>
       <c r="I117" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="J117" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="118">
@@ -35882,22 +35894,22 @@
         <v>0.27</v>
       </c>
       <c r="E118" s="198" t="n">
-        <v>0.2700710900473934</v>
+        <v>0.295</v>
       </c>
       <c r="F118" s="198" t="n">
-        <v>0.2223933649289101</v>
+        <v>0.295</v>
       </c>
       <c r="G118" s="198" t="n">
-        <v>0.2527843601895735</v>
+        <v>0.2808776886620489</v>
       </c>
       <c r="H118" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I118" s="198" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="J118" s="198" t="n">
-        <v>0.4527843601895736</v>
+        <v>0.4108776886620489</v>
       </c>
     </row>
     <row r="119"/>
@@ -35906,7 +35918,7 @@
       <c r="A121" s="188" t="inlineStr"/>
       <c r="B121" s="189" t="inlineStr">
         <is>
-          <t>Lenta</t>
+          <t>Magnit &amp; Dixy</t>
         </is>
       </c>
       <c r="C121" s="190" t="inlineStr">
@@ -36004,13 +36016,13 @@
         <v>0</v>
       </c>
       <c r="E123" s="195" t="n">
-        <v>0.1</v>
+        <v>0.08507109004739344</v>
       </c>
       <c r="F123" s="195" t="n">
-        <v>0.1</v>
+        <v>0.04739336492891005</v>
       </c>
       <c r="G123" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.03421436383521696</v>
       </c>
       <c r="H123" s="195" t="n">
         <v>0</v>
@@ -36019,7 +36031,7 @@
         <v>0</v>
       </c>
       <c r="J123" s="196" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.03421436383521696</v>
       </c>
     </row>
     <row r="124">
@@ -36076,13 +36088,13 @@
         <v>0</v>
       </c>
       <c r="E125" s="195" t="n">
-        <v>0.1</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F125" s="195" t="n">
-        <v>0.1</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="G125" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04538461538461539</v>
       </c>
       <c r="H125" s="195" t="n">
         <v>0</v>
@@ -36091,7 +36103,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="196" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04538461538461539</v>
       </c>
     </row>
     <row r="126">
@@ -36160,10 +36172,10 @@
         <v>0</v>
       </c>
       <c r="I127" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="J127" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="128">
@@ -36175,22 +36187,22 @@
         <v>0.27</v>
       </c>
       <c r="E128" s="198" t="n">
-        <v>0.295</v>
+        <v>0.2700710900473934</v>
       </c>
       <c r="F128" s="198" t="n">
-        <v>0.295</v>
+        <v>0.2223933649289101</v>
       </c>
       <c r="G128" s="198" t="n">
-        <v>0.2808776886620489</v>
+        <v>0.2527843601895735</v>
       </c>
       <c r="H128" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I128" s="198" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="J128" s="198" t="n">
-        <v>0.4808776886620489</v>
+        <v>0.3827843601895735</v>
       </c>
     </row>
     <row r="129"/>
@@ -36199,7 +36211,7 @@
       <c r="A131" s="188" t="inlineStr"/>
       <c r="B131" s="189" t="inlineStr">
         <is>
-          <t>HMs</t>
+          <t>Lenta</t>
         </is>
       </c>
       <c r="C131" s="190" t="inlineStr">
@@ -36300,10 +36312,10 @@
         <v>0.1</v>
       </c>
       <c r="F133" s="195" t="n">
-        <v>0.07742890995260657</v>
+        <v>0.1</v>
       </c>
       <c r="G133" s="195" t="n">
-        <v>0.04690120306234048</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="H133" s="195" t="n">
         <v>0</v>
@@ -36312,7 +36324,7 @@
         <v>0</v>
       </c>
       <c r="J133" s="196" t="n">
-        <v>0.04690120306234048</v>
+        <v>0.05384615384615385</v>
       </c>
     </row>
     <row r="134">
@@ -36453,10 +36465,10 @@
         <v>0</v>
       </c>
       <c r="I137" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="J137" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="138">
@@ -36471,19 +36483,19 @@
         <v>0.295</v>
       </c>
       <c r="F138" s="198" t="n">
-        <v>0.2724289099526066</v>
+        <v>0.295</v>
       </c>
       <c r="G138" s="198" t="n">
-        <v>0.2739327378782355</v>
+        <v>0.2808776886620489</v>
       </c>
       <c r="H138" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I138" s="198" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="J138" s="198" t="n">
-        <v>0.4739327378782355</v>
+        <v>0.4108776886620489</v>
       </c>
     </row>
     <row r="139"/>
@@ -36492,7 +36504,7 @@
       <c r="A141" s="188" t="inlineStr"/>
       <c r="B141" s="189" t="inlineStr">
         <is>
-          <t>OMNI</t>
+          <t>HMs</t>
         </is>
       </c>
       <c r="C141" s="190" t="inlineStr">
@@ -36593,10 +36605,10 @@
         <v>0.1</v>
       </c>
       <c r="F143" s="195" t="n">
-        <v>0.1</v>
+        <v>0.07742890995260657</v>
       </c>
       <c r="G143" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04690120306234048</v>
       </c>
       <c r="H143" s="195" t="n">
         <v>0</v>
@@ -36605,7 +36617,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="196" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04690120306234048</v>
       </c>
     </row>
     <row r="144">
@@ -36746,10 +36758,10 @@
         <v>0</v>
       </c>
       <c r="I147" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="J147" s="196" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="148">
@@ -36764,19 +36776,312 @@
         <v>0.295</v>
       </c>
       <c r="F148" s="198" t="n">
+        <v>0.2724289099526066</v>
+      </c>
+      <c r="G148" s="198" t="n">
+        <v>0.2739327378782355</v>
+      </c>
+      <c r="H148" s="198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="198" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J148" s="198" t="n">
+        <v>0.4039327378782355</v>
+      </c>
+    </row>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151">
+      <c r="A151" s="188" t="inlineStr"/>
+      <c r="B151" s="189" t="inlineStr">
+        <is>
+          <t>OMNI</t>
+        </is>
+      </c>
+      <c r="C151" s="190" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D151" s="190" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E151" s="190" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F151" s="190" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="G151" s="190" t="inlineStr">
+        <is>
+          <t>FY(100%)</t>
+        </is>
+      </c>
+      <c r="H151" s="190" t="inlineStr">
+        <is>
+          <t>Add Bonus</t>
+        </is>
+      </c>
+      <c r="I151" s="190" t="inlineStr">
+        <is>
+          <t>FY (200%)</t>
+        </is>
+      </c>
+      <c r="J151" s="190" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="191" t="inlineStr">
+        <is>
+          <t>KPI 1</t>
+        </is>
+      </c>
+      <c r="B152" s="191" t="inlineStr">
+        <is>
+          <t>NSV Total</t>
+        </is>
+      </c>
+      <c r="C152" s="192" t="n">
+        <v>0.1388033175355451</v>
+      </c>
+      <c r="D152" s="192" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E152" s="192" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F152" s="192" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G152" s="192" t="n">
+        <v>0.09356999635435656</v>
+      </c>
+      <c r="H152" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" s="193" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J152" s="193" t="n">
+        <v>0.1235699963543566</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="194" t="inlineStr">
+        <is>
+          <t>KPI 2</t>
+        </is>
+      </c>
+      <c r="B153" s="194" t="inlineStr">
+        <is>
+          <t>NSV Team</t>
+        </is>
+      </c>
+      <c r="C153" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="195" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F153" s="195" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G153" s="195" t="n">
+        <v>0.05384615384615385</v>
+      </c>
+      <c r="H153" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="196" t="n">
+        <v>0.05384615384615385</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="191" t="inlineStr">
+        <is>
+          <t>KPI 3</t>
+        </is>
+      </c>
+      <c r="B154" s="191" t="inlineStr">
+        <is>
+          <t>LSV/t Total</t>
+        </is>
+      </c>
+      <c r="C154" s="192" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D154" s="192" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E154" s="192" t="n">
+        <v>0.04500000000000001</v>
+      </c>
+      <c r="F154" s="192" t="n">
+        <v>0.04500000000000001</v>
+      </c>
+      <c r="G154" s="192" t="n">
+        <v>0.07961538461538462</v>
+      </c>
+      <c r="H154" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" s="193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="193" t="n">
+        <v>0.07961538461538462</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="194" t="inlineStr">
+        <is>
+          <t>KPI 4</t>
+        </is>
+      </c>
+      <c r="B155" s="194" t="inlineStr">
+        <is>
+          <t>LSV/t Team</t>
+        </is>
+      </c>
+      <c r="C155" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" s="195" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F155" s="195" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G155" s="195" t="n">
+        <v>0.05384615384615385</v>
+      </c>
+      <c r="H155" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" s="196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="196" t="n">
+        <v>0.05384615384615385</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="191" t="inlineStr">
+        <is>
+          <t>KPI 5</t>
+        </is>
+      </c>
+      <c r="B156" s="191" t="inlineStr">
+        <is>
+          <t>Earnings</t>
+        </is>
+      </c>
+      <c r="C156" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" s="193" t="n">
+        <v>0.06999999999999999</v>
+      </c>
+      <c r="J156" s="193" t="n">
+        <v>0.06999999999999999</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="194" t="inlineStr">
+        <is>
+          <t>KPI 6</t>
+        </is>
+      </c>
+      <c r="B157" s="194" t="inlineStr">
+        <is>
+          <t>Nsv Prem + Total</t>
+        </is>
+      </c>
+      <c r="C157" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" s="196" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J157" s="196" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="197" t="inlineStr"/>
+      <c r="C158" s="198" t="n">
+        <v>0.2588033175355451</v>
+      </c>
+      <c r="D158" s="198" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E158" s="198" t="n">
         <v>0.295</v>
       </c>
-      <c r="G148" s="198" t="n">
+      <c r="F158" s="198" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="G158" s="198" t="n">
         <v>0.2808776886620489</v>
       </c>
-      <c r="H148" s="198" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" s="198" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J148" s="198" t="n">
-        <v>0.4808776886620489</v>
+      <c r="H158" s="198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" s="198" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J158" s="198" t="n">
+        <v>0.4108776886620489</v>
       </c>
     </row>
   </sheetData>
@@ -36790,7 +37095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="161" min="1" max="1"/>
@@ -37032,13 +37337,13 @@
         <v>1.012215930166424</v>
       </c>
       <c r="P4" s="209" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q4" s="206" t="n">
-        <v>0.8987179487179489</v>
+        <v>0.03</v>
+      </c>
+      <c r="Q4" s="204" t="n">
+        <v>1.098717948717949</v>
       </c>
       <c r="R4" s="210" t="n">
-        <v>0.2696153846153846</v>
+        <v>0.3296153846153846</v>
       </c>
     </row>
     <row r="5">
@@ -37082,11 +37387,11 @@
       <c r="N5" s="202" t="n"/>
       <c r="O5" s="202" t="n"/>
       <c r="P5" s="202" t="n"/>
-      <c r="Q5" s="206" t="n">
-        <v>0.8858245230283145</v>
+      <c r="Q5" s="204" t="n">
+        <v>1.085824523028315</v>
       </c>
       <c r="R5" s="210" t="n">
-        <v>0.2657473569084943</v>
+        <v>0.3257473569084943</v>
       </c>
     </row>
     <row r="6">
@@ -37130,11 +37435,11 @@
       <c r="N6" s="202" t="n"/>
       <c r="O6" s="202" t="n"/>
       <c r="P6" s="202" t="n"/>
-      <c r="Q6" s="206" t="n">
-        <v>0.9012820512820513</v>
+      <c r="Q6" s="204" t="n">
+        <v>1.101282051282051</v>
       </c>
       <c r="R6" s="210" t="n">
-        <v>0.2703846153846154</v>
+        <v>0.3303846153846154</v>
       </c>
     </row>
     <row r="7">
@@ -37178,11 +37483,11 @@
       <c r="N7" s="202" t="n"/>
       <c r="O7" s="202" t="n"/>
       <c r="P7" s="202" t="n"/>
-      <c r="Q7" s="206" t="n">
-        <v>0.8551282051282052</v>
+      <c r="Q7" s="204" t="n">
+        <v>1.055128205128205</v>
       </c>
       <c r="R7" s="210" t="n">
-        <v>0.2565384615384615</v>
+        <v>0.3165384615384615</v>
       </c>
     </row>
     <row r="8">
@@ -37226,11 +37531,11 @@
       <c r="N8" s="202" t="n"/>
       <c r="O8" s="202" t="n"/>
       <c r="P8" s="202" t="n"/>
-      <c r="Q8" s="206" t="n">
-        <v>0.8910256410256411</v>
+      <c r="Q8" s="204" t="n">
+        <v>1.091025641025641</v>
       </c>
       <c r="R8" s="210" t="n">
-        <v>0.2673076923076923</v>
+        <v>0.3273076923076923</v>
       </c>
     </row>
     <row r="9">
@@ -37274,11 +37579,11 @@
       <c r="N9" s="202" t="n"/>
       <c r="O9" s="202" t="n"/>
       <c r="P9" s="202" t="n"/>
-      <c r="Q9" s="206" t="n">
-        <v>0.908974358974359</v>
+      <c r="Q9" s="204" t="n">
+        <v>1.108974358974359</v>
       </c>
       <c r="R9" s="210" t="n">
-        <v>0.2726923076923077</v>
+        <v>0.3326923076923077</v>
       </c>
     </row>
     <row r="10">
@@ -37322,11 +37627,11 @@
       <c r="N10" s="202" t="n"/>
       <c r="O10" s="202" t="n"/>
       <c r="P10" s="202" t="n"/>
-      <c r="Q10" s="206" t="n">
-        <v>0.9012820512820513</v>
+      <c r="Q10" s="204" t="n">
+        <v>1.101282051282051</v>
       </c>
       <c r="R10" s="210" t="n">
-        <v>0.2703846153846154</v>
+        <v>0.3303846153846154</v>
       </c>
     </row>
     <row r="11">
@@ -37374,11 +37679,11 @@
       <c r="N11" s="202" t="n"/>
       <c r="O11" s="202" t="n"/>
       <c r="P11" s="202" t="n"/>
-      <c r="Q11" s="206" t="n">
-        <v>0.908974358974359</v>
+      <c r="Q11" s="204" t="n">
+        <v>1.108974358974359</v>
       </c>
       <c r="R11" s="210" t="n">
-        <v>0.2726923076923077</v>
+        <v>0.3326923076923077</v>
       </c>
     </row>
     <row r="12">
@@ -37422,11 +37727,11 @@
       <c r="N12" s="202" t="n"/>
       <c r="O12" s="202" t="n"/>
       <c r="P12" s="202" t="n"/>
-      <c r="Q12" s="206" t="n">
-        <v>0.8153299307327746</v>
+      <c r="Q12" s="204" t="n">
+        <v>1.015329930732775</v>
       </c>
       <c r="R12" s="210" t="n">
-        <v>0.2445989792198324</v>
+        <v>0.3045989792198324</v>
       </c>
     </row>
     <row r="13">
@@ -37470,11 +37775,11 @@
       <c r="N13" s="202" t="n"/>
       <c r="O13" s="202" t="n"/>
       <c r="P13" s="202" t="n"/>
-      <c r="Q13" s="206" t="n">
-        <v>0.908974358974359</v>
+      <c r="Q13" s="204" t="n">
+        <v>1.108974358974359</v>
       </c>
       <c r="R13" s="210" t="n">
-        <v>0.2726923076923077</v>
+        <v>0.3326923076923077</v>
       </c>
     </row>
     <row r="14">
@@ -37518,11 +37823,11 @@
       <c r="N14" s="202" t="n"/>
       <c r="O14" s="202" t="n"/>
       <c r="P14" s="202" t="n"/>
-      <c r="Q14" s="206" t="n">
-        <v>0.8858245230283145</v>
+      <c r="Q14" s="204" t="n">
+        <v>1.085824523028315</v>
       </c>
       <c r="R14" s="210" t="n">
-        <v>0.2657473569084943</v>
+        <v>0.3257473569084943</v>
       </c>
     </row>
     <row r="15">
@@ -37567,10 +37872,10 @@
       <c r="O15" s="202" t="n"/>
       <c r="P15" s="202" t="n"/>
       <c r="Q15" s="206" t="n">
-        <v>0.6730769230769231</v>
+        <v>0.8730769230769231</v>
       </c>
       <c r="R15" s="210" t="n">
-        <v>0.2019230769230769</v>
+        <v>0.2619230769230769</v>
       </c>
     </row>
     <row r="16">
@@ -37614,11 +37919,11 @@
       <c r="N16" s="202" t="n"/>
       <c r="O16" s="202" t="n"/>
       <c r="P16" s="202" t="n"/>
-      <c r="Q16" s="206" t="n">
-        <v>0.908974358974359</v>
+      <c r="Q16" s="204" t="n">
+        <v>1.108974358974359</v>
       </c>
       <c r="R16" s="210" t="n">
-        <v>0.2726923076923077</v>
+        <v>0.3326923076923077</v>
       </c>
     </row>
     <row r="17">
@@ -37663,10 +37968,10 @@
       <c r="O17" s="202" t="n"/>
       <c r="P17" s="202" t="n"/>
       <c r="Q17" s="206" t="n">
-        <v>0.7346882974845061</v>
+        <v>0.9346882974845061</v>
       </c>
       <c r="R17" s="210" t="n">
-        <v>0.2204064892453518</v>
+        <v>0.2804064892453518</v>
       </c>
     </row>
     <row r="18">
@@ -37711,59 +38016,98 @@
       <c r="O18" s="202" t="n"/>
       <c r="P18" s="202" t="n"/>
       <c r="Q18" s="206" t="n">
-        <v>0.7294871794871796</v>
+        <v>0.9294871794871795</v>
       </c>
       <c r="R18" s="210" t="n">
-        <v>0.2188461538461539</v>
+        <v>0.2788461538461539</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="199" t="n"/>
-      <c r="B19" s="211" t="inlineStr">
+      <c r="B19" s="200" t="inlineStr">
         <is>
           <t>Total PN</t>
         </is>
       </c>
-      <c r="C19" s="212" t="n">
+      <c r="C19" s="211" t="n">
         <v>1.012977411325948</v>
       </c>
-      <c r="D19" s="213" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E19" s="212" t="n">
+      <c r="D19" s="212" t="n">
+        <v>0.05384615384615385</v>
+      </c>
+      <c r="E19" s="213" t="n">
         <v>0.997896799895361</v>
       </c>
-      <c r="F19" s="213" t="n">
-        <v>0.04500000000000001</v>
-      </c>
-      <c r="G19" s="212" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="H19" s="213" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="I19" s="212" t="n">
+      <c r="F19" s="212" t="n">
+        <v>0.04846153846153847</v>
+      </c>
+      <c r="G19" s="213" t="n">
+        <v>0.6576923076923078</v>
+      </c>
+      <c r="H19" s="210" t="n">
+        <v>0.1973076923076923</v>
+      </c>
+      <c r="I19" s="211" t="n">
         <v>1.012977411325948</v>
       </c>
-      <c r="J19" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="212" t="n">
+      <c r="J19" s="214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="213" t="n">
         <v>0.997896799895361</v>
       </c>
-      <c r="L19" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="214" t="n"/>
-      <c r="N19" s="215" t="n"/>
-      <c r="O19" s="214" t="n"/>
-      <c r="P19" s="215" t="n"/>
-      <c r="Q19" s="212" t="n">
-        <v>1.283333333333333</v>
-      </c>
-      <c r="R19" s="213" t="n">
-        <v>0.385</v>
-      </c>
+      <c r="L19" s="214" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="199" t="n"/>
+      <c r="N19" s="199" t="n"/>
+      <c r="O19" s="199" t="n"/>
+      <c r="P19" s="199" t="n"/>
+      <c r="Q19" s="211" t="n">
+        <v>1.091025641025641</v>
+      </c>
+      <c r="R19" s="210" t="n">
+        <v>0.3273076923076923</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="215" t="inlineStr">
+        <is>
+          <t>Total Target</t>
+        </is>
+      </c>
+      <c r="C20" s="216" t="n">
+        <v>1.012977411325948</v>
+      </c>
+      <c r="D20" s="217" t="n">
+        <v>0.09356999635435656</v>
+      </c>
+      <c r="E20" s="216" t="n">
+        <v>0.997896799895361</v>
+      </c>
+      <c r="F20" s="217" t="n">
+        <v>0.07961538461538462</v>
+      </c>
+      <c r="G20" s="218" t="n"/>
+      <c r="H20" s="219" t="n"/>
+      <c r="I20" s="216" t="n">
+        <v>1.012977411325948</v>
+      </c>
+      <c r="J20" s="217" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K20" s="216" t="n">
+        <v>0.997896799895361</v>
+      </c>
+      <c r="L20" s="217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="218" t="n"/>
+      <c r="N20" s="219" t="n"/>
+      <c r="O20" s="218" t="n"/>
+      <c r="P20" s="219" t="n"/>
+      <c r="Q20" s="218" t="n"/>
+      <c r="R20" s="219" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -37779,9 +38123,9 @@
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="A4:A10"/>
     <mergeCell ref="M4:M18"/>
-    <mergeCell ref="A11:A18"/>
     <mergeCell ref="O4:O18"/>
     <mergeCell ref="P4:P18"/>
+    <mergeCell ref="A11:A19"/>
     <mergeCell ref="C1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
